--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Sportello Unico per le Attività Produttive (SUAP).xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Sportello Unico per le Attività Produttive (SUAP).xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="96">
   <si>
     <r>
       <t xml:space="preserve">
@@ -722,7 +722,7 @@
     <t>Aggiungi documenti</t>
   </si>
   <si>
-    <t>-</t>
+    <t>Consulta la pratica</t>
   </si>
   <si>
     <t>Paga (inserito automaticamente dall'app se il messaggio prevede un avviso di pagamento pagoPA)</t>
@@ -745,13 +745,16 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
       <t xml:space="preserve">
 File allegato al messaggio</t>
     </r>
+  </si>
+  <si>
+    <t>-</t>
   </si>
   <si>
     <r>
@@ -813,14 +816,6 @@
       </rPr>
       <t>Note aggiuntive</t>
     </r>
-  </si>
-  <si>
-    <t>✨ Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi della scadenza tramite notifica push.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promemoria automatici — Messaggi Premium
-Impostando il messaggio di Avviso di pagamento come Messaggio Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, non è necessario inviare il seguente messaggio di promemoria.
-Gli utenti che hanno dato il loro consenso, infatti, riceveranno automaticamente una notifica push sui loro dispositivi all’avvicinarsi della scadenza.</t>
   </si>
 </sst>
 </file>
@@ -1524,7 +1519,7 @@
         <v>80</v>
       </c>
       <c r="G6" s="34" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1555,73 +1550,73 @@
         <v>82</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G9" s="34" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G10" s="34" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>56</v>
@@ -1633,10 +1628,10 @@
         <v>56</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="G11" s="34" t="s">
         <v>56</v>
